--- a/docs/bug-report/BugReport_QAPractice.xlsx
+++ b/docs/bug-report/BugReport_QAPractice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DVDSTORE\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_798FEFB33C3C7B0DD8ADC3EB8BBCB23D7041CD76" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1234F435-944B-45C8-92A1-992A3451885F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
   <si>
     <t>Bug_ID</t>
   </si>
@@ -57,121 +57,118 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Linked TC_ID</t>
+    <t>Linked TC_IDs</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>BUG-001</t>
-  </si>
-  <si>
-    <t>Album placeholder links non-functional</t>
-  </si>
-  <si>
-    <t>Iframe/Album</t>
+    <t>BUG-01</t>
+  </si>
+  <si>
+    <t>Iframe Album placeholder links/buttons are non-functional</t>
+  </si>
+  <si>
+    <t>Iframe / Album</t>
   </si>
   <si>
     <t>Major</t>
   </si>
   <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>1. Open Iframe page. 2. Switch into the album iframe. 3. Click 'Follow on Twitter','Like on Facebook','Email me','Album', or any card 'View'/'Edit'.</t>
+  </si>
+  <si>
+    <t>Each link/button navigates to its destination or performs its action.</t>
+  </si>
+  <si>
+    <t>All are &lt;a href="#"&gt; placeholders; clicking neither navigates nor performs any action.</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>TC-035, TC-036, TC-037, TC-038, TC-041, TC-042</t>
+  </si>
+  <si>
+    <t>6 requirement-driven negative tests assert intended behavior and FAIL by design (all in IframeTest): test_9_2_Iframe_TwitterLink, _FacebookLink, _EmailLink, _AlbumLink, _ViewButtons_AllCards, _EditButtons_AllCards.</t>
+  </si>
+  <si>
+    <t>BUG-02</t>
+  </si>
+  <si>
+    <t>PracticeFormPage.selectHobby switched on wrong values</t>
+  </si>
+  <si>
+    <t>Practice form</t>
+  </si>
+  <si>
+    <t>1. Call selectHobby() for Sports/Reading/Music. 2. Observe which control toggles.</t>
+  </si>
+  <si>
+    <t>selectHobby targets the Sports/Reading/Music checkboxes.</t>
+  </si>
+  <si>
+    <t>selectHobby switched on Male/Female/Other (gender) instead of the hobby checkboxes.</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>TC-061</t>
+  </si>
+  <si>
+    <t>Fixed during development. Retained for history.</t>
+  </si>
+  <si>
+    <t>BUG-03</t>
+  </si>
+  <si>
+    <t>PracticeFormPage.selectCity opened the State dropdown</t>
+  </si>
+  <si>
+    <t>1. Call selectCity() to pick a city. 2. Observe which dropdown opens.</t>
+  </si>
+  <si>
+    <t>selectCity opens the City dropdown.</t>
+  </si>
+  <si>
+    <t>selectCity opened the State dropdown instead of City.</t>
+  </si>
+  <si>
+    <t>TC-062</t>
+  </si>
+  <si>
+    <t>BUG-04</t>
+  </si>
+  <si>
+    <t>Fixed ad-banner (#fixedban) intercepted clicks</t>
+  </si>
+  <si>
+    <t>Practice form / Automation</t>
+  </si>
+  <si>
+    <t>Minor</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>1. Open Iframe page. 2. Switch into album iframe. 3. Click 'Follow on Twitter', 'Like on Facebook', 'Email me', 'Album', or any card's View/Edit.</t>
-  </si>
-  <si>
-    <t>Each link/button navigates to its target or performs its action.</t>
-  </si>
-  <si>
-    <t>All are href="#"; clicking does not navigate or perform any action.</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>TC-033, TC-035</t>
-  </si>
-  <si>
-    <t>Demo-site placeholders; logged as requirement-driven negative finding.</t>
-  </si>
-  <si>
-    <t>BUG-002</t>
-  </si>
-  <si>
-    <t>PracticeForm hobby/city wiring bug</t>
-  </si>
-  <si>
-    <t>Practice form</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>1. Open practice form. 2. selectHobby() switched on gender values. 3. selectCity() opened the State dropdown.</t>
-  </si>
-  <si>
-    <t>selectHobby targets Sports/Reading/Music; selectCity opens the City dropdown.</t>
-  </si>
-  <si>
-    <t>selectHobby switched on Male/Female/Other; selectCity opened the State dropdown.</t>
-  </si>
-  <si>
-    <t>Closed</t>
-  </si>
-  <si>
-    <t>TC-058, TC-059</t>
-  </si>
-  <si>
-    <t>Historical defect; FIXED by developer. Retained for traceability/history.</t>
-  </si>
-  <si>
-    <t>BUG-003</t>
-  </si>
-  <si>
-    <t>Mobile-number length not validated</t>
-  </si>
-  <si>
-    <t>Minor</t>
-  </si>
-  <si>
-    <t>1. Open practice form. 2. Enter mobile '123' (under 10) or '12345678901' (over 10). 3. Submit.</t>
-  </si>
-  <si>
-    <t>Form rejects mobile numbers that are not exactly 10 digits.</t>
-  </si>
-  <si>
-    <t>TBD on run - verify whether short/long values are rejected; if accepted, this is a validation gap.</t>
-  </si>
-  <si>
-    <t>TC-055, TC-056</t>
-  </si>
-  <si>
-    <t>Watch item: confirm behavior during execution before final triage.</t>
-  </si>
-  <si>
-    <t>BUG-004</t>
-  </si>
-  <si>
-    <t>Navbar links non-functional</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>1. Open Iframe page. 2. Switch into iframe. 3. Click navbar items.</t>
-  </si>
-  <si>
-    <t>Navbar links route to social/email/album destinations.</t>
-  </si>
-  <si>
-    <t>Navbar links are placeholders and do not route (subset of BUG-001 pattern).</t>
-  </si>
-  <si>
-    <t>TC-033</t>
-  </si>
-  <si>
-    <t>Inferred; consolidate with BUG-001 if treated as one defect.</t>
+    <t>1. Open practice form. 2. Attempt to click Submit or a dropdown near the banner.</t>
+  </si>
+  <si>
+    <t>Submit and dropdown clicks reach their targets.</t>
+  </si>
+  <si>
+    <t>The fixed #fixedban banner overlapped the form and intercepted Submit/dropdown clicks.</t>
+  </si>
+  <si>
+    <t>TC-058, TC-059, TC-070</t>
+  </si>
+  <si>
+    <t>Automation/environment issue. Fixed by hiding #fixedban via JS. Mobile-field validation is correct and is NOT a defect.</t>
   </si>
 </sst>
 </file>
@@ -199,7 +196,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -210,6 +207,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF2E5496"/>
         <bgColor rgb="FF666699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4E4"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFFCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -240,12 +249,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -274,7 +289,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFFCE4E4"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -290,7 +305,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -515,17 +530,17 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="32" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="32" customWidth="1"/>
+    <col min="8" max="8" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="47.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -563,7 +578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="66" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -588,7 +603,7 @@
       <c r="H2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J2" s="2" t="s">
@@ -612,95 +627,95 @@
         <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="I4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="K4" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
